--- a/products/pack2-proposal-toolkit/section-lm-decoder.xlsx
+++ b/products/pack2-proposal-toolkit/section-lm-decoder.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -101,8 +101,41 @@
       <color rgb="FF01696F"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -121,8 +154,13 @@
         <bgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,6 +183,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -156,7 +208,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -248,6 +300,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,7 +329,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -297,6 +369,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -546,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="16" min="1" max="1"/>
@@ -558,9 +641,9 @@
     <col width="10" customWidth="1" style="16" min="8" max="8"/>
     <col width="30" customWidth="1" style="16" min="9" max="10"/>
     <col width="14" customWidth="1" style="16" min="11" max="12"/>
+    <col width="16" customWidth="1" style="17" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="17">
       <c r="B2" s="18" t="inlineStr">
         <is>
@@ -575,7 +658,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="36" customHeight="1" s="17">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -632,6 +714,11 @@
       <c r="L5" s="20" t="inlineStr">
         <is>
           <t>Draft Status</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>Weight (numeric)</t>
         </is>
       </c>
     </row>
@@ -663,6 +750,7 @@
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="23" t="n"/>
+      <c r="M6" s="32" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1" s="17">
       <c r="B7" s="24" t="inlineStr">
@@ -718,6 +806,9 @@
           <t>Not Started</t>
         </is>
       </c>
+      <c r="M7" s="33" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1" s="17">
       <c r="B8" s="24" t="inlineStr">
@@ -773,6 +864,9 @@
           <t>Not Started</t>
         </is>
       </c>
+      <c r="M8" s="33" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1" s="17">
       <c r="B9" s="24" t="inlineStr">
@@ -827,6 +921,9 @@
         <is>
           <t>Not Started</t>
         </is>
+      </c>
+      <c r="M9" s="33" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="17">
@@ -857,6 +954,7 @@
       <c r="J10" s="22" t="n"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="23" t="n"/>
+      <c r="M10" s="32" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1" s="17">
       <c r="B11" s="24" t="inlineStr">
@@ -912,6 +1010,9 @@
           <t>Not Started</t>
         </is>
       </c>
+      <c r="M11" s="33" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="17">
       <c r="B12" s="24" t="inlineStr">
@@ -967,6 +1068,9 @@
         <is>
           <t>Not Started</t>
         </is>
+      </c>
+      <c r="M12" s="33" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="17">
@@ -997,6 +1101,9 @@
       <c r="J13" s="22" t="n"/>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="23" t="n"/>
+      <c r="M13" s="33" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14" ht="48" customHeight="1" s="17">
       <c r="B14" s="24" t="inlineStr">
@@ -1054,6 +1161,7 @@
           <t>Not Started</t>
         </is>
       </c>
+      <c r="M14" s="32" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1" s="17">
       <c r="B15" s="24" t="inlineStr">
@@ -1110,6 +1218,7 @@
           <t>Not Started</t>
         </is>
       </c>
+      <c r="M15" s="32" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1" s="17">
       <c r="B16" s="24" t="inlineStr">
@@ -1170,15 +1279,31 @@
           <t>Not Started</t>
         </is>
       </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="M16" s="33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="L18" s="34" t="inlineStr">
+        <is>
+          <t>WEIGHT TOTAL</t>
+        </is>
+      </c>
+      <c r="M18" s="35">
+        <f>SUM(M7:M16)</f>
+        <v/>
+      </c>
+    </row>
     <row r="19" ht="27.75" customHeight="1" s="17">
       <c r="B19" s="27" t="inlineStr">
         <is>
           <t>COMMON EVALUATION CRITERIA PATTERNS BY ACQUISITION TYPE</t>
         </is>
       </c>
+      <c r="M19" s="36">
+        <f>IF(ROUND(M18,4)=1,"Totals 100%","CHECK — does not total 100%")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="31.5" customHeight="1" s="17">
       <c r="B20" s="20" t="inlineStr">
@@ -1219,6 +1344,11 @@
       <c r="I20" s="20" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="L20" s="37" t="inlineStr">
+        <is>
+          <t>Past Performance carries its weight at the parent row (M-3) because its sub-factors are confidence-rated, not numerically weighted. Enter weights where Section M assigns them, then confirm the total reads 100%.</t>
         </is>
       </c>
     </row>
@@ -1531,6 +1661,11 @@
     </cfRule>
     <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
       <formula>"Not Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>LEFT(M19,5)="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -1556,14 +1691,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="16" min="1" max="1"/>
     <col width="90" customWidth="1" style="16" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="17">
       <c r="B2" s="18" t="inlineStr">
         <is>
@@ -1578,8 +1712,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="21.75" customHeight="1" s="17">
       <c r="B6" s="29" t="inlineStr">
         <is>
@@ -1594,7 +1726,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="17">
       <c r="B9" s="29" t="inlineStr">
         <is>
@@ -1644,7 +1775,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="21.75" customHeight="1" s="17">
       <c r="B17" s="29" t="inlineStr">
         <is>
@@ -1659,7 +1789,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="18" customHeight="1" s="17">
       <c r="B20" s="30" t="inlineStr">
         <is>
@@ -1702,7 +1831,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="31.5" customHeight="1" s="17">
       <c r="B27" s="30" t="inlineStr">
         <is>
@@ -1710,7 +1838,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="21.75" customHeight="1" s="17">
       <c r="B29" s="29" t="inlineStr">
         <is>
@@ -1753,7 +1880,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="17">
       <c r="B36" s="29" t="inlineStr">
         <is>
@@ -1789,11 +1915,24 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="18" customHeight="1" s="17">
       <c r="B42" s="30" t="inlineStr">
         <is>
           <t>© Acqlerate — Defense Acquisitions Academy. For training use only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="38" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>

--- a/products/pack2-proposal-toolkit/section-lm-decoder.xlsx
+++ b/products/pack2-proposal-toolkit/section-lm-decoder.xlsx
@@ -8,9 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L-M Decoder" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phrase Decoder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phrase Decoder'!$B$5:$G$37</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -134,8 +137,38 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -157,6 +190,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +246,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -320,6 +358,36 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -329,7 +397,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -380,6 +448,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6F2F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1686,6 +1761,1002 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" style="17" min="1" max="1"/>
+    <col width="7" customWidth="1" style="17" min="2" max="2"/>
+    <col width="40" customWidth="1" style="17" min="3" max="3"/>
+    <col width="44" customWidth="1" style="17" min="4" max="4"/>
+    <col width="44" customWidth="1" style="17" min="5" max="5"/>
+    <col width="44" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="17" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="40" t="inlineStr">
+        <is>
+          <t>Phrase Decoder: What the RFP Says vs. What It Means</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>32 phrases that appear in nearly every DoD Section L and M, decoded. Filter by section. Mark the ones in your RFP and hand this to the writing team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>L / M</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>What the RFP says</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>What it actually means</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>The mistake people make</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>In my RFP?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1" s="17">
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>"Offerors will be evaluated on the degree to which..."</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>A graded scale, not pass/fail. "Degree" means there is a top score and you are competing for it.</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>Write to Outstanding, not Acceptable. Quantify everything. Give the evaluator a reason to write "exceeds."</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>Answering the requirement without exceeding it. Acceptable loses to Outstanding every time on a best-value award.</t>
+        </is>
+      </c>
+      <c r="G6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1" s="17">
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>"...demonstrates a clear understanding of the requirement."</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>They want proof you have done this before and know where it goes wrong. Restating the PWS is not understanding.</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>Name the two or three things that make this requirement hard, and say how you handle each. Cite a past contract where you did.</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>Parroting the PWS back with "we understand" in front of it. Evaluators call this "compliant but empty."</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1" s="17">
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>"...the extent to which the approach is feasible / realistic."</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>They suspect offerors will over-promise. Feasibility is scored, and unrealistic staffing or schedule gets marked down even if the narrative is strong.</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>Show the math. Hours by task, staffing ramp, schedule with float. Tie it to your price volume so the two agree.</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>Technical volume promises 24/7 coverage; price volume staffs one shift. The cost/price analyst catches it and both volumes get dinged.</t>
+        </is>
+      </c>
+      <c r="G8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="78" customHeight="1" s="17">
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>"...will be evaluated for strengths, weaknesses, significant weaknesses, and deficiencies."</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>This is the FAR 15.001 vocabulary. A deficiency makes you unawardable. A significant weakness "appreciably increases risk." Strengths are what win.</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>Structure every section so strengths are easy to find: bold the discriminator, state the benefit to the government, give the proof.</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>Burying the strength in paragraph four. Evaluators are reading forty proposals; make it findable.</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="n"/>
+    </row>
+    <row r="10" ht="78" customHeight="1" s="17">
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>"Risk will be assessed as part of each factor."</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>There is no separate risk factor, but every factor carries a risk rating. A great approach with high risk can lose to a good approach with low risk.</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>For each factor, name the top risk and your mitigation in one paragraph. Use the words "risk" and "mitigation."</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>Ignoring risk because there is no risk factor. The evaluator still has to fill in a risk rating and will find one for you.</t>
+        </is>
+      </c>
+      <c r="G10" s="45" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1" s="17">
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>"Past performance will be evaluated for recency, relevance, and quality."</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>Three separate tests. A great reference that is not recent or not relevant scores as if it were not there.</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>Pick references that pass all three. Recent means inside the RFP window (usually 3 to 5 years). Relevant means same size, scope, and complexity. Quality means the CPARS or PPQ says so.</t>
+        </is>
+      </c>
+      <c r="F11" s="48" t="inlineStr">
+        <is>
+          <t>Leading with your biggest contract. If it is not relevant to this work, it is a wasted reference slot.</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1" s="17">
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>"Offerors without a record of relevant past performance ... will receive a neutral rating."</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>Neutral is not a gift. In a competitive field, neutral loses to Substantial Confidence. The FAR says neutral cannot hurt you; it does not say it helps.</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>If you are thin on relevant past performance, use subcontractor or key personnel references, and say so explicitly in the past performance volume.</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>Assuming neutral is fine. Against an incumbent with Substantial Confidence, it is not.</t>
+        </is>
+      </c>
+      <c r="G12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="78" customHeight="1" s="17">
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>"Price will be evaluated for reasonableness and realism."</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>Two different tests. Reasonableness: is it too high? Realism: is it too low to actually do the work? A low price fails realism and can be adjusted upward for evaluation.</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="inlineStr">
+        <is>
+          <t>Price to win, but never below what your technical volume requires. Show your basis of estimate. Run the Cost Realism Self-Check in this pack.</t>
+        </is>
+      </c>
+      <c r="F13" s="48" t="inlineStr">
+        <is>
+          <t>Buying in. A price the government does not believe gets adjusted up on paper, and you lose the price advantage you cut margin for.</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="n"/>
+    </row>
+    <row r="14" ht="78" customHeight="1" s="17">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>"...best value tradeoff."</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>The government may pay more for a better proposal. Price matters, but it is not the tiebreaker unless technical proposals are close.</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Decide early whether you are the technical leader or the price leader. Write the whole proposal around that choice.</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>Trying to be both. You end up mid-pack on technical and not cheap enough to win on price.</t>
+        </is>
+      </c>
+      <c r="G14" s="45" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1" s="17">
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>"...lowest price technically acceptable (LPTA)."</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
+        <is>
+          <t>Technical is pass/fail. Once you pass, only price matters. Extra strengths are worth zero.</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="inlineStr">
+        <is>
+          <t>Write to the minimum acceptable standard, cleanly, and put every dollar of effort into price. Do not gold-plate.</t>
+        </is>
+      </c>
+      <c r="F15" s="48" t="inlineStr">
+        <is>
+          <t>Writing an Outstanding technical volume for an LPTA award. You spent money on words that could not score.</t>
+        </is>
+      </c>
+      <c r="G15" s="49" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1" s="17">
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>"...non-price factors, when combined, are significantly more important than price."</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>The government has told you the weighting. "Significantly more important" is the strongest phrasing. A technically superior proposal can win at a real price premium.</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Invest in technical and past performance. Do not shave margin to compete on price; compete on being obviously better.</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>Reading "significantly more important" and still pricing to the floor. You gave away margin you did not need to.</t>
+        </is>
+      </c>
+      <c r="G16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="78" customHeight="1" s="17">
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>"...approximately equal to price."</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>Price is a peer of the technical factors, not subordinate. A modest technical edge will not survive a large price gap.</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>Price tight. Make sure every strength is a discriminator the evaluator can defend in the source selection decision document.</t>
+        </is>
+      </c>
+      <c r="F17" s="48" t="inlineStr">
+        <is>
+          <t>Assuming technical wins. Under "approximately equal," a 15% price gap usually decides it.</t>
+        </is>
+      </c>
+      <c r="G17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1" s="17">
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>"...the Government intends to award without discussions."</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>You get one shot. There will be no clarification round to fix a gap or explain an ambiguity.</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>Assume no discussions. Every requirement answered, every assumption stated, price fully supported on submission.</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>Leaving something thin and planning to fix it in discussions. Under FAR 15.306, there may not be any.</t>
+        </is>
+      </c>
+      <c r="G18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1" s="17">
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>"...the Government reserves the right to conduct discussions."</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="inlineStr">
+        <is>
+          <t>They probably will, but only with the competitive range. Falling out of the range is a silent loss.</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="inlineStr">
+        <is>
+          <t>Submit as if there will be no discussions, then be ready to answer evaluation notices fast and completely.</t>
+        </is>
+      </c>
+      <c r="F19" s="48" t="inlineStr">
+        <is>
+          <t>Treating the initial submission as a draft. The competitive range is set from initial proposals.</t>
+        </is>
+      </c>
+      <c r="G19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="78" customHeight="1" s="17">
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>"Key personnel will be evaluated on qualifications and availability."</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Availability is a real test. A resume for someone who might not show up on day one is a weakness, sometimes a significant one.</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>Signed letters of commitment. Resumes that match the labor category requirements line by line. Name the backfill.</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>Proposing a star you have not signed. If the evaluator asks and you cannot produce a commitment letter, that is a weakness.</t>
+        </is>
+      </c>
+      <c r="G20" s="45" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1" s="17">
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>"...resumes shall demonstrate..."</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>The evaluator will check each named qualification against the resume. Missing one is a gap.</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="inlineStr">
+        <is>
+          <t>Build the resume from the RFP requirement list, in that order, with the qualification stated in the same words.</t>
+        </is>
+      </c>
+      <c r="F21" s="48" t="inlineStr">
+        <is>
+          <t>Sending the candidate's standard resume. It answers a different question.</t>
+        </is>
+      </c>
+      <c r="G21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="78" customHeight="1" s="17">
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>"...Small Business Participation will be evaluated."</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>This is a scored factor for large businesses, separate from the subcontracting plan. Goals you commit to here become contract terms.</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Commit to percentages you can hit, name the small businesses, and describe how you will track it.</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>Committing to 40% to score well, then failing to deliver. That becomes a CPARS finding and a past performance problem on the next bid.</t>
+        </is>
+      </c>
+      <c r="G22" s="45" t="n"/>
+    </row>
+    <row r="23" ht="78" customHeight="1" s="17">
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>"Transition plan will be evaluated for risk to continuity of service."</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>On a recompete, the incumbent has a built-in advantage: zero transition risk. You have to prove yours is nearly zero too.</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="inlineStr">
+        <is>
+          <t>A day-by-day plan for the first 30 days with names, a knowledge capture approach, and the incumbent-capture strategy.</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="inlineStr">
+        <is>
+          <t>A one-page "we will work closely with the incumbent" transition plan. That is a significant weakness against an incumbent.</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="78" customHeight="1" s="17">
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>"Proposals shall be submitted in separate volumes..."</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>Cross-referencing between volumes is usually prohibited. Each volume is evaluated by different people who may never see the others.</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>Make every volume self-contained. If price needs a technical assumption, restate it in the price volume.</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>Writing "see Technical Volume, section 3" in the price volume. The price evaluator never sees it.</t>
+        </is>
+      </c>
+      <c r="G24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="78" customHeight="1" s="17">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>"Page limits are ... Pages exceeding the limit will not be evaluated."</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>Not "may not." The pages are removed before evaluation. Anything on page 31 of a 30-page limit does not exist.</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="inlineStr">
+        <is>
+          <t>Build a page budget by volume (Compliance Matrix in this pack does it). Cut before submission, never after.</t>
+        </is>
+      </c>
+      <c r="F25" s="48" t="inlineStr">
+        <is>
+          <t>Assuming the cover page or table of contents is excluded. Read the definition of "page" in Section L; it usually is not.</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="78" customHeight="1" s="17">
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>"...12-point font, 1-inch margins, 8.5 x 11..."</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>Format compliance is checked first, before anyone reads a word. Violations can be treated as non-responsive.</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>A format checklist at the end of every review cycle. One person owns it.</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>Shrinking tables to 8-point to fit. Section L usually specifies font size for tables and graphics too.</t>
+        </is>
+      </c>
+      <c r="G26" s="45" t="n"/>
+    </row>
+    <row r="27" ht="78" customHeight="1" s="17">
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>"...shall not merely restate the requirement or state that the offeror understands."</t>
+        </is>
+      </c>
+      <c r="D27" s="48" t="inlineStr">
+        <is>
+          <t>The government has been burned by empty proposals and is pre-emptively disqualifying them.</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="inlineStr">
+        <is>
+          <t>Every paragraph: what we will do, how, why it works, proof it has worked. If a paragraph does not contain a verb the government can evaluate, delete it.</t>
+        </is>
+      </c>
+      <c r="F27" s="48" t="inlineStr">
+        <is>
+          <t>"Offeror understands and will comply." That sentence is now a weakness by instruction.</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="78" customHeight="1" s="17">
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>"Offerors shall address each element of the PWS..."</t>
+        </is>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>The evaluator has a checklist with every PWS paragraph. Missing one is a gap, and gaps become deficiencies.</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>Compliance matrix mapped PWS paragraph by paragraph to your section and page. Fill every row before pink team.</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>Addressing the PWS by theme instead of by paragraph. The evaluator is not reading by theme.</t>
+        </is>
+      </c>
+      <c r="G28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="78" customHeight="1" s="17">
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>"...assumptions and exceptions shall be clearly identified."</t>
+        </is>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>An unstated assumption is a risk finding when discovered. A stated exception to the terms can make you non-responsive. Both are traps.</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="inlineStr">
+        <is>
+          <t>State assumptions in one labeled section per volume. Take no exceptions to the terms unless you are prepared to lose on them.</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>Burying an assumption in the pricing narrative. When it surfaces, it reads as concealment.</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="78" customHeight="1" s="17">
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>"...oral presentations will be conducted."</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>The orals are scored. Your presenters are being evaluated as the people who will do the work.</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>Rehearse with the actual key personnel who will present. Prepare for questions, not just the pitch.</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>Sending the capture manager to present. The government wants to hear from the PM they will be working with.</t>
+        </is>
+      </c>
+      <c r="G30" s="45" t="n"/>
+    </row>
+    <row r="31" ht="78" customHeight="1" s="17">
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>"...the Government will not reimburse proposal preparation costs."</t>
+        </is>
+      </c>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>Standard, but it means your B&amp;P is at risk. The bid/no-bid decision is a real financial decision.</t>
+        </is>
+      </c>
+      <c r="E31" s="48" t="inlineStr">
+        <is>
+          <t>Run a formal bid/no-bid with a probability of win estimate before spending on the proposal.</t>
+        </is>
+      </c>
+      <c r="F31" s="48" t="inlineStr">
+        <is>
+          <t>Bidding everything. Losing proposals cost the same to write as winning ones.</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="78" customHeight="1" s="17">
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>"Questions must be submitted by ... and will be answered by amendment."</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>Answers become part of the RFP. Other offerors see your question. A question can reveal your strategy.</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>Ask questions that clarify requirements. Do not ask questions that reveal your approach or fish for a competitor's weakness.</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>Asking "would the government accept X?" You just told every competitor you plan to do X.</t>
+        </is>
+      </c>
+      <c r="G32" s="45" t="n"/>
+    </row>
+    <row r="33" ht="78" customHeight="1" s="17">
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>"Offerors shall acknowledge all amendments."</t>
+        </is>
+      </c>
+      <c r="D33" s="48" t="inlineStr">
+        <is>
+          <t>Failure to acknowledge an amendment can make the proposal non-responsive, regardless of quality.</t>
+        </is>
+      </c>
+      <c r="E33" s="48" t="inlineStr">
+        <is>
+          <t>A line item on the submission checklist, owned by the contracts manager. Check SAM.gov the morning of submission.</t>
+        </is>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
+        <is>
+          <t>Assuming no amendments were issued. There is almost always at least one.</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="78" customHeight="1" s="17">
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>"...electronic submission via ... by [time] [time zone]."</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Late is late. There is no grace period, and the time zone is the government's, not yours.</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Submit the day before. Confirm receipt in writing. Keep the confirmation.</t>
+        </is>
+      </c>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>Submitting at 4:58 for a 5:00 deadline. Upload portals fail under load on due dates.</t>
+        </is>
+      </c>
+      <c r="G34" s="45" t="n"/>
+    </row>
+    <row r="35" ht="78" customHeight="1" s="17">
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C35" s="47" t="inlineStr">
+        <is>
+          <t>"Section L instructions do not change the requirements of the PWS."</t>
+        </is>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>Section L tells you how to write; the PWS tells you what to do. When they seem to conflict, the PWS controls.</t>
+        </is>
+      </c>
+      <c r="E35" s="48" t="inlineStr">
+        <is>
+          <t>Read the PWS first, then Section L, then Section M. Build the compliance matrix from all three.</t>
+        </is>
+      </c>
+      <c r="F35" s="48" t="inlineStr">
+        <is>
+          <t>Writing to Section L headings and missing a PWS requirement that Section L did not mention.</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="n"/>
+    </row>
+    <row r="36" ht="78" customHeight="1" s="17">
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>"Strengths must be tied to a benefit to the Government."</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>A feature is not a strength. A strength is a feature plus a stated benefit to the government that exceeds the requirement.</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>Every discriminator in three parts: what we do, what the government gets, why it is better than the standard. Use the Win Theme tool.</t>
+        </is>
+      </c>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>Listing capabilities. "We have an ISO 9001 certified quality system" is a feature. What does the government get from it?</t>
+        </is>
+      </c>
+      <c r="G36" s="45" t="n"/>
+    </row>
+    <row r="37" ht="78" customHeight="1" s="17">
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
+        <is>
+          <t>"...will be evaluated for the offeror's ability to retain qualified staff."</t>
+        </is>
+      </c>
+      <c r="D37" s="48" t="inlineStr">
+        <is>
+          <t>Retention is scored because turnover is the number-one delivery risk on services contracts. They want a retention plan, not a hiring plan.</t>
+        </is>
+      </c>
+      <c r="E37" s="48" t="inlineStr">
+        <is>
+          <t>Retention rate over the last three years, the compensation and career approach that produces it, and the retention plan for this contract.</t>
+        </is>
+      </c>
+      <c r="F37" s="48" t="inlineStr">
+        <is>
+          <t>A recruiting plan when the RFP asked about retention. Different question.</t>
+        </is>
+      </c>
+      <c r="G37" s="49" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="50" t="inlineStr">
+        <is>
+          <t>Phrases in my RFP:</t>
+        </is>
+      </c>
+      <c r="C39" s="51">
+        <f>COUNTIF(G6:G37,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>Acqlerate Proposal Toolkit · acqlerate.com · September 2026 Edition</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="B5:G37"/>
+  <conditionalFormatting sqref="B6:G37">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>$G6="Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G6:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF0D1B2A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
